--- a/artfynd/A 31896-2021 artfynd.xlsx
+++ b/artfynd/A 31896-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31896-2021 artfynd.xlsx
+++ b/artfynd/A 31896-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114477620</v>
+        <v>114477613</v>
       </c>
       <c r="B2" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>1106</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,12 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418637</v>
+        <v>418590</v>
       </c>
       <c r="R2" t="n">
-        <v>6587096</v>
+        <v>6587094</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -795,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114477613</v>
+        <v>114477642</v>
       </c>
       <c r="B3" t="n">
-        <v>90532</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1106</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,7 +820,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -844,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418590</v>
+        <v>418562</v>
       </c>
       <c r="R3" t="n">
-        <v>6587094</v>
+        <v>6587093</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,37 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119440629</v>
+        <v>114477683</v>
       </c>
       <c r="B4" t="n">
-        <v>42956</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100679</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brun gräsfjäril</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coenonympha hero</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,23 +933,24 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Steffensminne, Vrm</t>
+          <t>Iland, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418270</v>
+        <v>418658</v>
       </c>
       <c r="R4" t="n">
-        <v>6587746</v>
+        <v>6587107</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,27 +969,17 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Karlstad</t>
+          <t>Alster</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,14 +999,1182 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119440629</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43450</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Steffensminne, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>418270</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6587746</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
           <t>Åsa Weiss</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Karlstad kommun - Brungräsfjäril stockfallet</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118012120</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43251</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102923</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettkantad guldvinge</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycaena hippothoe</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>418721</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6587035</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114477636</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>418313</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6587462</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114477620</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>418637</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6587096</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114477622</v>
+      </c>
+      <c r="B9" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>418619</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6587120</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114477623</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>418568</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6587105</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114477696</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>418459</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6587439</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-11-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-11-10</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114477701</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>418566</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6587122</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-11-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Karlstads kommun - NVI Steffensminne</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>93419750</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långenäsvägen,Karlstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>418481</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6587244</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kevin Ward</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kevin Ward, Anneli Brändén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125508499</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Iland, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>418680</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6587075</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Matilda Elgerud</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
